--- a/site/downloads/buy-sell-hold-calculator.xlsx
+++ b/site/downloads/buy-sell-hold-calculator.xlsx
@@ -566,7 +566,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Built by Lone Star Exotics Hub (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
+          <t>Built by Exotic Ranch &amp; Wildlife Network (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
         </is>
       </c>
     </row>
